--- a/comunidades_anuros.xlsx
+++ b/comunidades_anuros.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a51e1d9e0f733e61/Documentos/aula_ecologia_de_campo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_F25DC773A252ABDACC10482C51DE550A5BDE58E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{699DCC59-67FD-431A-ADC6-564DD6963F81}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="11_F25DC773A252ABDACC10482C51DE550A5BDE58E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D501C112-65A7-4CE6-AEDE-8091906ECED0}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,7 +447,24 @@
   <dimension ref="A1:R15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
